--- a/10_Threshold_OUTPUT/direct_Q92PW3_Sinorhizobium_meliloti_1021.xlsx
+++ b/10_Threshold_OUTPUT/direct_Q92PW3_Sinorhizobium_meliloti_1021.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,15 +446,25 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>full_pattern</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>group1</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>group2</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>full_pattern_html</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>p_value</t>
         </is>
@@ -477,15 +487,25 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>TCTTGATTTGTT</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>ATTTGTT</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>TCTTGAT</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;C&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;G&lt;/span&gt;&lt;span style="color: purple; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: purple; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;G&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>0.2818872451019592</v>
       </c>
     </row>
@@ -506,15 +526,25 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>TGTTCTTGATTTGTTC</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>TGTTC</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>TGTTC</t>
         </is>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;G&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;C&lt;/span&gt;TTGATT&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;G&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;C&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
         <v>0.02019192323070772</v>
       </c>
     </row>
@@ -535,15 +565,25 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>TGTTCTTGAT</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>TGAT</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>TGTT</t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;G&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;CT&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;G&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
         <v>0.911235505797681</v>
       </c>
     </row>
@@ -564,15 +604,25 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>TTCTTGATTT</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>TTT</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>TTC</t>
         </is>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;C&lt;/span&gt;TTGA&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
         <v>0.9426229508196722</v>
       </c>
     </row>
@@ -593,15 +643,25 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>ATTT</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>TTT</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>ATT</t>
         </is>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: purple; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: purple; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
         <v>0.9900039984006398</v>
       </c>
     </row>
@@ -622,15 +682,25 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>TTTGTTC</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t>TTC</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>TTT</t>
         </is>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;G&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;C&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
         <v>0.994202319072371</v>
       </c>
     </row>
@@ -651,15 +721,25 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
+          <t>TTCTTGATTTGTTCT</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t>TCT</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>TTC</t>
         </is>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;C&lt;/span&gt;TTGATTTGT&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;C&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
         <v>0.9994002399040384</v>
       </c>
     </row>
@@ -680,15 +760,25 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
+          <t>TTCT</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t>TCT</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>TTC</t>
         </is>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: purple; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: purple; font-weight: bold;"&gt;C&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
         <v>0.9998000799680128</v>
       </c>
     </row>
@@ -709,15 +799,25 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
+          <t>TTC</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t>TC</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>TT</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>TT</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: purple; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;C&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
         <v>0.9998000799680128</v>
       </c>
     </row>
@@ -738,15 +838,25 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
+          <t>TTCT</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
           <t>CT</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>TT</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>TT</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;C&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
         <v>0.9998000799680128</v>
       </c>
     </row>
@@ -767,7 +877,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>TT</t>
+          <t>TTCTT</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -775,7 +885,17 @@
           <t>TT</t>
         </is>
       </c>
-      <c r="G12" t="n">
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>TT</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;C&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
         <v>0.9998000799680128</v>
       </c>
     </row>
@@ -796,15 +916,25 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
+          <t>ATGTTCTTGAT</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
           <t>AT</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>AT</t>
         </is>
       </c>
-      <c r="G13" t="n">
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;GTTCTTG&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
         <v>0.9998000799680128</v>
       </c>
     </row>
@@ -825,15 +955,25 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
+          <t>TTGAT</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
           <t>AT</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>TT</t>
-        </is>
-      </c>
-      <c r="G14" t="n">
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>TT</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;G&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
         <v>0.9998000799680128</v>
       </c>
     </row>
@@ -854,7 +994,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>TT</t>
+          <t>TTGATT</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -862,7 +1002,17 @@
           <t>TT</t>
         </is>
       </c>
-      <c r="G15" t="n">
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>TT</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;GA&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
         <v>0.9998000799680128</v>
       </c>
     </row>
@@ -883,7 +1033,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>TT</t>
+          <t>TTCTTGATTT</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -891,7 +1041,17 @@
           <t>TT</t>
         </is>
       </c>
-      <c r="G16" t="n">
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>TT</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;CTTGAT&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
         <v>0.9762095161935226</v>
       </c>
     </row>
@@ -912,15 +1072,25 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>TT</t>
+          <t>ATTT</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
+          <t>TT</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
           <t>AT</t>
         </is>
       </c>
-      <c r="G17" t="n">
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
         <v>0.9966013594562175</v>
       </c>
     </row>
@@ -941,15 +1111,25 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>TT</t>
+          <t>TCTTGATTTGTT</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
+          <t>TT</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
           <t>TC</t>
         </is>
       </c>
-      <c r="G18" t="n">
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;C&lt;/span&gt;TTGATTTG&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
         <v>0.9998000799680128</v>
       </c>
     </row>
@@ -970,7 +1150,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>TT</t>
+          <t>TTGATTTGTT</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -978,7 +1158,17 @@
           <t>TT</t>
         </is>
       </c>
-      <c r="G19" t="n">
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>TT</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;GATTTG&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
         <v>0.9998000799680128</v>
       </c>
     </row>
@@ -999,7 +1189,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>TT</t>
+          <t>TTGTT</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1007,7 +1197,17 @@
           <t>TT</t>
         </is>
       </c>
-      <c r="G20" t="n">
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>TT</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;G&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
         <v>0.9850059976009596</v>
       </c>
     </row>
@@ -1028,15 +1228,25 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
+          <t>ATTTGTTC</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
           <t>TC</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>AT</t>
         </is>
       </c>
-      <c r="G21" t="n">
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;TTGT&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;C&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
         <v>0.9998000799680128</v>
       </c>
     </row>
@@ -1057,15 +1267,25 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
+          <t>TTCTTGATTTGTTCT</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
           <t>CT</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>TT</t>
-        </is>
-      </c>
-      <c r="G22" t="n">
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>TT</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;CTTGATTTGTT&lt;span style="color: blue; font-weight: bold;"&gt;C&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
         <v>0.9998000799680128</v>
       </c>
     </row>
@@ -1086,15 +1306,25 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
+          <t>TGTTCTTGATTTGTTCTG</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
           <t>TG</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>TG</t>
         </is>
       </c>
-      <c r="G23" t="n">
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;G&lt;/span&gt;TTCTTGATTTGTTC&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;G&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
         <v>0.9998000799680128</v>
       </c>
     </row>
@@ -1115,15 +1345,25 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
+          <t>TGTTCTG</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
           <t>TG</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>TG</t>
         </is>
       </c>
-      <c r="G24" t="n">
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;G&lt;/span&gt;TTC&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;G&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
         <v>0.9998000799680128</v>
       </c>
     </row>

--- a/10_Threshold_OUTPUT/direct_Q92PW3_Sinorhizobium_meliloti_1021.xlsx
+++ b/10_Threshold_OUTPUT/direct_Q92PW3_Sinorhizobium_meliloti_1021.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:J24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,6 +469,11 @@
           <t>p_value</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>evaluation</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -508,6 +513,11 @@
       <c r="I2" t="n">
         <v>0.2818872451019592</v>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Ambiguous DR</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -547,6 +557,11 @@
       <c r="I3" t="n">
         <v>0.02019192323070772</v>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
@@ -585,6 +600,11 @@
       </c>
       <c r="I4" t="n">
         <v>0.911235505797681</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Ambiguous DR</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -625,6 +645,11 @@
       <c r="I5" t="n">
         <v>0.9426229508196722</v>
       </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Ambiguous DR</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
@@ -664,6 +689,11 @@
       <c r="I6" t="n">
         <v>0.9900039984006398</v>
       </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Ambiguous DR</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
@@ -703,6 +733,11 @@
       <c r="I7" t="n">
         <v>0.994202319072371</v>
       </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Ambiguous DR</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
@@ -742,6 +777,11 @@
       <c r="I8" t="n">
         <v>0.9994002399040384</v>
       </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Ambiguous DR</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
@@ -781,6 +821,11 @@
       <c r="I9" t="n">
         <v>0.9998000799680128</v>
       </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Ambiguous DR</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
@@ -820,6 +865,11 @@
       <c r="I10" t="n">
         <v>0.9998000799680128</v>
       </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Ambiguous DR</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
@@ -859,6 +909,11 @@
       <c r="I11" t="n">
         <v>0.9998000799680128</v>
       </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Ambiguous DR</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
@@ -898,6 +953,11 @@
       <c r="I12" t="n">
         <v>0.9998000799680128</v>
       </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
@@ -937,6 +997,11 @@
       <c r="I13" t="n">
         <v>0.9998000799680128</v>
       </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
@@ -976,6 +1041,11 @@
       <c r="I14" t="n">
         <v>0.9998000799680128</v>
       </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Ambiguous DR</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
@@ -1015,6 +1085,11 @@
       <c r="I15" t="n">
         <v>0.9998000799680128</v>
       </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
@@ -1054,6 +1129,11 @@
       <c r="I16" t="n">
         <v>0.9762095161935226</v>
       </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
@@ -1093,6 +1173,11 @@
       <c r="I17" t="n">
         <v>0.9966013594562175</v>
       </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Ambiguous DR</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
@@ -1132,6 +1217,11 @@
       <c r="I18" t="n">
         <v>0.9998000799680128</v>
       </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Ambiguous DR</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
@@ -1171,6 +1261,11 @@
       <c r="I19" t="n">
         <v>0.9998000799680128</v>
       </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
@@ -1210,6 +1305,11 @@
       <c r="I20" t="n">
         <v>0.9850059976009596</v>
       </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
@@ -1249,6 +1349,11 @@
       <c r="I21" t="n">
         <v>0.9998000799680128</v>
       </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Ambiguous DR</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
@@ -1288,6 +1393,11 @@
       <c r="I22" t="n">
         <v>0.9998000799680128</v>
       </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Ambiguous DR</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
@@ -1327,6 +1437,11 @@
       <c r="I23" t="n">
         <v>0.9998000799680128</v>
       </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
@@ -1365,6 +1480,11 @@
       </c>
       <c r="I24" t="n">
         <v>0.9998000799680128</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/10_Threshold_OUTPUT/direct_Q92PW3_Sinorhizobium_meliloti_1021.xlsx
+++ b/10_Threshold_OUTPUT/direct_Q92PW3_Sinorhizobium_meliloti_1021.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J24"/>
+  <dimension ref="A1:K24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -474,6 +474,11 @@
           <t>evaluation</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>correctness_%</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -518,6 +523,9 @@
           <t>Ambiguous DR</t>
         </is>
       </c>
+      <c r="K2" t="n">
+        <v>57.14</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -562,6 +570,9 @@
           <t>Confirmed DR</t>
         </is>
       </c>
+      <c r="K3" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
@@ -606,6 +617,9 @@
           <t>Ambiguous DR</t>
         </is>
       </c>
+      <c r="K4" t="n">
+        <v>75</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
@@ -650,6 +664,9 @@
           <t>Ambiguous DR</t>
         </is>
       </c>
+      <c r="K5" t="n">
+        <v>66.67</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
@@ -694,6 +711,9 @@
           <t>Ambiguous DR</t>
         </is>
       </c>
+      <c r="K6" t="n">
+        <v>66.67</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
@@ -738,6 +758,9 @@
           <t>Ambiguous DR</t>
         </is>
       </c>
+      <c r="K7" t="n">
+        <v>66.67</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
@@ -782,6 +805,9 @@
           <t>Ambiguous DR</t>
         </is>
       </c>
+      <c r="K8" t="n">
+        <v>33.33</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
@@ -826,6 +852,9 @@
           <t>Ambiguous DR</t>
         </is>
       </c>
+      <c r="K9" t="n">
+        <v>33.33</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
@@ -870,6 +899,9 @@
           <t>Ambiguous DR</t>
         </is>
       </c>
+      <c r="K10" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
@@ -914,6 +946,9 @@
           <t>Ambiguous DR</t>
         </is>
       </c>
+      <c r="K11" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
@@ -958,6 +993,9 @@
           <t>Confirmed DR</t>
         </is>
       </c>
+      <c r="K12" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
@@ -1002,6 +1040,9 @@
           <t>Confirmed DR</t>
         </is>
       </c>
+      <c r="K13" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
@@ -1046,6 +1087,9 @@
           <t>Ambiguous DR</t>
         </is>
       </c>
+      <c r="K14" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
@@ -1090,6 +1134,9 @@
           <t>Confirmed DR</t>
         </is>
       </c>
+      <c r="K15" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
@@ -1134,6 +1181,9 @@
           <t>Confirmed DR</t>
         </is>
       </c>
+      <c r="K16" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
@@ -1178,6 +1228,9 @@
           <t>Ambiguous DR</t>
         </is>
       </c>
+      <c r="K17" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
@@ -1222,6 +1275,9 @@
           <t>Ambiguous DR</t>
         </is>
       </c>
+      <c r="K18" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
@@ -1266,6 +1322,9 @@
           <t>Confirmed DR</t>
         </is>
       </c>
+      <c r="K19" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
@@ -1310,6 +1369,9 @@
           <t>Confirmed DR</t>
         </is>
       </c>
+      <c r="K20" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
@@ -1354,6 +1416,9 @@
           <t>Ambiguous DR</t>
         </is>
       </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
@@ -1398,6 +1463,9 @@
           <t>Ambiguous DR</t>
         </is>
       </c>
+      <c r="K22" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
@@ -1442,6 +1510,9 @@
           <t>Confirmed DR</t>
         </is>
       </c>
+      <c r="K23" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
@@ -1485,6 +1556,9 @@
         <is>
           <t>Confirmed DR</t>
         </is>
+      </c>
+      <c r="K24" t="n">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
